--- a/static/data/exports/Retro_AS_GE_2014.xlsx
+++ b/static/data/exports/Retro_AS_GE_2014.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Retro Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/static/data/exports/Retro_AS_GE_2014.xlsx
+++ b/static/data/exports/Retro_AS_GE_2014.xlsx
@@ -8662,11 +8662,11 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E133" t="n">
         <v>1996</v>
@@ -9778,11 +9778,11 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E151" t="n">
         <v>2073</v>
@@ -10894,11 +10894,11 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E169" t="n">
         <v>3023</v>
@@ -12320,11 +12320,11 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D192" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E192" t="n">
         <v>965</v>
@@ -13312,11 +13312,11 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E208" t="n">
         <v>752</v>
@@ -14242,11 +14242,11 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E223" t="n">
         <v>2273</v>
@@ -15420,11 +15420,11 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E242" t="n">
         <v>1376</v>
@@ -27076,11 +27076,11 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D430" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E430" t="n">
         <v>2540</v>
@@ -28502,11 +28502,11 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D453" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E453" t="n">
         <v>3545</v>
@@ -29680,11 +29680,11 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D472" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E472" t="n">
         <v>948</v>
@@ -34197,11 +34197,11 @@
     </row>
     <row r="545">
       <c r="A545" t="n">
-        <v>1723341</v>
+        <v>1723342</v>
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Kashem Ali Akonda</t>
+          <t>Monirul Hussain</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
@@ -34234,7 +34234,7 @@
       </c>
       <c r="K545" t="inlineStr">
         <is>
-          <t>Kashem Ali Akonda</t>
+          <t>Monirul Hussain</t>
         </is>
       </c>
       <c r="L545" t="inlineStr">
@@ -34259,11 +34259,11 @@
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>1723342</v>
+        <v>1723341</v>
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Monirul Hussain</t>
+          <t>Kashem Ali Akonda</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
@@ -34296,7 +34296,7 @@
       </c>
       <c r="K546" t="inlineStr">
         <is>
-          <t>Monirul Hussain</t>
+          <t>Kashem Ali Akonda</t>
         </is>
       </c>
       <c r="L546" t="inlineStr">
@@ -35446,11 +35446,11 @@
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D565" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E565" t="n">
         <v>2953</v>
@@ -36624,11 +36624,11 @@
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D584" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E584" t="n">
         <v>1568</v>
@@ -37430,11 +37430,11 @@
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D597" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E597" t="n">
         <v>4609</v>
@@ -38546,11 +38546,11 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D615" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E615" t="n">
         <v>1258</v>
@@ -39414,11 +39414,11 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D629" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E629" t="n">
         <v>6443</v>
@@ -40468,11 +40468,11 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D646" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E646" t="n">
         <v>1822</v>
@@ -47961,11 +47961,11 @@
     </row>
     <row r="767">
       <c r="A767" t="n">
-        <v>1723564</v>
+        <v>1723563</v>
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>Md. Zakir Hussain</t>
+          <t>Dr. Faruk Aahammed Bhuyan</t>
         </is>
       </c>
       <c r="C767" t="inlineStr">
@@ -47998,7 +47998,7 @@
       </c>
       <c r="K767" t="inlineStr">
         <is>
-          <t>Md. Zakir Hussain</t>
+          <t>Dr. Faruk Aahammed Bhuyan</t>
         </is>
       </c>
       <c r="L767" t="inlineStr">
@@ -48023,11 +48023,11 @@
     </row>
     <row r="768">
       <c r="A768" t="n">
-        <v>1723563</v>
+        <v>1723564</v>
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>Dr. Faruk Aahammed Bhuyan</t>
+          <t>Md. Zakir Hussain</t>
         </is>
       </c>
       <c r="C768" t="inlineStr">
@@ -48060,7 +48060,7 @@
       </c>
       <c r="K768" t="inlineStr">
         <is>
-          <t>Dr. Faruk Aahammed Bhuyan</t>
+          <t>Md. Zakir Hussain</t>
         </is>
       </c>
       <c r="L768" t="inlineStr">
@@ -54852,11 +54852,11 @@
       </c>
       <c r="C878" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D878" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E878" t="n">
         <v>1853</v>
@@ -62416,11 +62416,11 @@
       </c>
       <c r="C1000" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1000" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E1000" t="n">
         <v>2469</v>
@@ -63098,11 +63098,11 @@
       </c>
       <c r="C1011" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1011" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E1011" t="n">
         <v>1504</v>
@@ -63718,11 +63718,11 @@
       </c>
       <c r="C1021" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1021" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E1021" t="n">
         <v>884</v>
@@ -64214,11 +64214,11 @@
       </c>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1029" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E1029" t="n">
         <v>6811</v>
@@ -64834,11 +64834,11 @@
       </c>
       <c r="C1039" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1039" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E1039" t="n">
         <v>7119</v>
@@ -65516,11 +65516,11 @@
       </c>
       <c r="C1050" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1050" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E1050" t="n">
         <v>2673</v>
@@ -66198,11 +66198,11 @@
       </c>
       <c r="C1061" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1061" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E1061" t="n">
         <v>1630</v>
@@ -66818,11 +66818,11 @@
       </c>
       <c r="C1071" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1071" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E1071" t="n">
         <v>1262</v>
@@ -88828,11 +88828,11 @@
       </c>
       <c r="C1426" t="inlineStr">
         <is>
-          <t>CPM</t>
+          <t>CPI(M)</t>
         </is>
       </c>
       <c r="D1426" t="n">
-        <v>19912</v>
+        <v>19875</v>
       </c>
       <c r="E1426" t="n">
         <v>555</v>
